--- a/StructureDefinition-Prov-Resurs-inom-halso--och-sjukvard.xlsx
+++ b/StructureDefinition-Prov-Resurs-inom-halso--och-sjukvard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Prov-Resurs-inom-halso--och-sjukvard.xlsx
+++ b/StructureDefinition-Prov-Resurs-inom-halso--och-sjukvard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Prov : Resurs (inom hälso- och sjukvård)).</t>
+    <t>(inom hälso- och sjukvården:) humanbiologiskt material som tagits från en levande eller avliden person eller ett foster i syfte att erhålla information om den som provet härrör från (Biobanksordlistan, under rev.)
+Exempel på humanbiologiskt material är vävnad och kroppsvätskor som blod, urin, sekret.</t>
   </si>
   <si>
     <t>Purpose</t>
